--- a/example.xlsx
+++ b/example.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Диплом\simple_forecaster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD44CFA1-FA0B-44CF-B75D-1F1EB68CA20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04510B30-C0A6-41FF-A346-AC96895929B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{CAA089E8-208D-4B4E-A3B3-B281B9E9FAB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +35,78 @@
   </si>
   <si>
     <t>unsold</t>
+  </si>
+  <si>
+    <t>hidden unsold</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>X4</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>X6</t>
+  </si>
+  <si>
+    <t>X7</t>
+  </si>
+  <si>
+    <t>X8</t>
+  </si>
+  <si>
+    <t>X9</t>
+  </si>
+  <si>
+    <t>X10</t>
+  </si>
+  <si>
+    <t>X11</t>
+  </si>
+  <si>
+    <t>X12</t>
+  </si>
+  <si>
+    <t>X13</t>
+  </si>
+  <si>
+    <t>X14</t>
+  </si>
+  <si>
+    <t>X15</t>
+  </si>
+  <si>
+    <t>X16</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -47,7 +120,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +164,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -106,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -142,6 +224,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -149,7 +246,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -166,6 +263,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -173,7 +279,377 @@
     <cellStyle name="Финансовый 2 2" xfId="3" xr:uid="{F5075C6B-1996-449E-B782-584FF0585696}"/>
     <cellStyle name="Финансовый 4" xfId="1" xr:uid="{7F0FA60E-3A20-421C-870D-2017C9C62AC7}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="22">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -521,15 +997,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B14312E-43B6-40B4-81C3-CBF4FB2044B7}">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,8 +1015,11 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>43831</v>
       </c>
@@ -550,8 +1029,11 @@
       <c r="C2" s="4">
         <v>37239888.210000031</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="4">
+        <v>26348080.890000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>43862</v>
       </c>
@@ -561,8 +1043,11 @@
       <c r="C3" s="4">
         <v>35597505.119999997</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3" s="4">
+        <v>24529580.670000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>43891</v>
       </c>
@@ -572,8 +1057,11 @@
       <c r="C4" s="4">
         <v>34680760.380000077</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4" s="4">
+        <v>22990357.039999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>43922</v>
       </c>
@@ -583,8 +1071,11 @@
       <c r="C5" s="4">
         <v>33980906.360000037</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5" s="4">
+        <v>22653181.620000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>43952</v>
       </c>
@@ -594,8 +1085,11 @@
       <c r="C6" s="4">
         <v>32930309.820000067</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6" s="4">
+        <v>24111721.27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>43983</v>
       </c>
@@ -605,8 +1099,11 @@
       <c r="C7" s="4">
         <v>33173815.219999917</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7" s="4">
+        <v>22191776.359999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>44013</v>
       </c>
@@ -616,8 +1113,11 @@
       <c r="C8" s="4">
         <v>32522434.090000048</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8" s="4">
+        <v>22664385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>44044</v>
       </c>
@@ -627,8 +1127,11 @@
       <c r="C9" s="4">
         <v>31781539.629999958</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9" s="4">
+        <v>21779319.120000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>44075</v>
       </c>
@@ -638,8 +1141,11 @@
       <c r="C10" s="4">
         <v>31043097.269999992</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10" s="4">
+        <v>21582178.760000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>44105</v>
       </c>
@@ -649,8 +1155,11 @@
       <c r="C11" s="4">
         <v>30345060.619999975</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11" s="4">
+        <v>21489094.460000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>44136</v>
       </c>
@@ -660,8 +1169,11 @@
       <c r="C12" s="4">
         <v>29567283.599999957</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12" s="4">
+        <v>21782330.940000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>44166</v>
       </c>
@@ -671,8 +1183,11 @@
       <c r="C13" s="4">
         <v>29422472.570000045</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13" s="4">
+        <v>20741011.100000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>44197</v>
       </c>
@@ -682,8 +1197,11 @@
       <c r="C14" s="4">
         <v>28403863.869999975</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14" s="4">
+        <v>23562683.969999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>44228</v>
       </c>
@@ -693,8 +1211,11 @@
       <c r="C15" s="4">
         <v>28636119.380000021</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15" s="4">
+        <v>20920680.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>44256</v>
       </c>
@@ -704,8 +1225,11 @@
       <c r="C16" s="4">
         <v>28819625.920000024</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" s="4">
+        <v>20141405.760000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>44287</v>
       </c>
@@ -715,8 +1239,11 @@
       <c r="C17" s="4">
         <v>29035093.310000025</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="4">
+        <v>19340934.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>44317</v>
       </c>
@@ -726,8 +1253,11 @@
       <c r="C18" s="4">
         <v>29655648.18000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="4">
+        <v>19826724.350000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>44348</v>
       </c>
@@ -737,8 +1267,11 @@
       <c r="C19" s="4">
         <v>30366840.890000019</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="4">
+        <v>19870260.800000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>44378</v>
       </c>
@@ -748,8 +1281,11 @@
       <c r="C20" s="4">
         <v>31428192.000000071</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20" s="4">
+        <v>20560847.280000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>44409</v>
       </c>
@@ -759,8 +1295,11 @@
       <c r="C21" s="4">
         <v>32650587.07</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21" s="4">
+        <v>21321816.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>44440</v>
       </c>
@@ -770,8 +1309,11 @@
       <c r="C22" s="4">
         <v>33981410.519999996</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22" s="4">
+        <v>20230487.68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>44470</v>
       </c>
@@ -781,8 +1323,11 @@
       <c r="C23" s="4">
         <v>35018775.389999926</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23" s="4">
+        <v>20019670.899999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>44501</v>
       </c>
@@ -792,8 +1337,11 @@
       <c r="C24" s="4">
         <v>35823418.009999998</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24" s="4">
+        <v>19511871.359999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>44531</v>
       </c>
@@ -803,8 +1351,11 @@
       <c r="C25" s="4">
         <v>36170775.279999942</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25" s="4">
+        <v>19375856.719999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>44562</v>
       </c>
@@ -814,8 +1365,11 @@
       <c r="C26" s="4">
         <v>36178514.940000057</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26" s="4">
+        <v>19653571.359999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>44593</v>
       </c>
@@ -825,8 +1379,11 @@
       <c r="C27" s="4">
         <v>35915173.079999976</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27" s="4">
+        <v>19781183.629999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>44621</v>
       </c>
@@ -836,8 +1393,11 @@
       <c r="C28" s="4">
         <v>35915828.460000031</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28" s="4">
+        <v>19833790.280000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>44652</v>
       </c>
@@ -847,8 +1407,11 @@
       <c r="C29" s="4">
         <v>35083633.969999984</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29" s="4">
+        <v>19517155.600000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>44682</v>
       </c>
@@ -858,8 +1421,11 @@
       <c r="C30" s="4">
         <v>35216119.93000003</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30" s="4">
+        <v>19753632.73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>44713</v>
       </c>
@@ -869,8 +1435,11 @@
       <c r="C31" s="4">
         <v>36277029.790000007</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31" s="4">
+        <v>20216316.829999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>44743</v>
       </c>
@@ -880,8 +1449,11 @@
       <c r="C32" s="4">
         <v>37681461.250000052</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32" s="4">
+        <v>21032088.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>44774</v>
       </c>
@@ -891,8 +1463,11 @@
       <c r="C33" s="4">
         <v>38713193.740000062</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33" s="4">
+        <v>21879596.969999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>44805</v>
       </c>
@@ -902,8 +1477,11 @@
       <c r="C34" s="4">
         <v>39824770.870000064</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34" s="4">
+        <v>22059732.93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>44835</v>
       </c>
@@ -913,8 +1491,11 @@
       <c r="C35" s="4">
         <v>40492051.530000076</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35" s="4">
+        <v>23118691.129999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>44866</v>
       </c>
@@ -924,8 +1505,11 @@
       <c r="C36" s="4">
         <v>41167136.870000057</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36" s="4">
+        <v>22872501.120000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>44896</v>
       </c>
@@ -935,8 +1519,11 @@
       <c r="C37" s="4">
         <v>42192094.700000122</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37" s="4">
+        <v>22829584.809999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>44927</v>
       </c>
@@ -946,8 +1533,11 @@
       <c r="C38" s="4">
         <v>42250842.170000114</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38" s="4">
+        <v>23314202.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>44958</v>
       </c>
@@ -957,8 +1547,11 @@
       <c r="C39" s="4">
         <v>41234984.230000064</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39" s="4">
+        <v>26523596.370000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>44986</v>
       </c>
@@ -968,8 +1561,11 @@
       <c r="C40" s="4">
         <v>41569823.25999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40" s="4">
+        <v>26940648.789999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>45017</v>
       </c>
@@ -979,8 +1575,11 @@
       <c r="C41" s="4">
         <v>43522802.119999968</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41" s="4">
+        <v>23574312.239999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>45047</v>
       </c>
@@ -990,8 +1589,11 @@
       <c r="C42" s="4">
         <v>44128439.129999928</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42" s="4">
+        <v>24015347.140000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>45078</v>
       </c>
@@ -1001,8 +1603,11 @@
       <c r="C43" s="4">
         <v>45525263.169999965</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43" s="4">
+        <v>22499656</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>45108</v>
       </c>
@@ -1012,8 +1617,11 @@
       <c r="C44" s="4">
         <v>45859790.08000008</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44" s="4">
+        <v>22709774.609999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>45139</v>
       </c>
@@ -1023,8 +1631,11 @@
       <c r="C45" s="4">
         <v>45814440.849999882</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45" s="4">
+        <v>22604519.539999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45170</v>
       </c>
@@ -1034,8 +1645,11 @@
       <c r="C46" s="4">
         <v>45678045.85999985</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46" s="4">
+        <v>22233831.760000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45200</v>
       </c>
@@ -1045,8 +1659,11 @@
       <c r="C47" s="4">
         <v>44977624.040000074</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47" s="4">
+        <v>22011766.370000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>45231</v>
       </c>
@@ -1056,8 +1673,11 @@
       <c r="C48" s="4">
         <v>44903751.499999911</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48" s="4">
+        <v>22591236.280000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>45261</v>
       </c>
@@ -1067,8 +1687,11 @@
       <c r="C49" s="4">
         <v>45351709.170000002</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49" s="4">
+        <v>22631709.699999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>45292</v>
       </c>
@@ -1078,8 +1701,11 @@
       <c r="C50" s="4">
         <v>46501419.450000107</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50" s="4">
+        <v>22305297.829999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>45323</v>
       </c>
@@ -1089,8 +1715,11 @@
       <c r="C51" s="4">
         <v>47022018.799999967</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51" s="4">
+        <v>21510898.890000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>45352</v>
       </c>
@@ -1100,8 +1729,11 @@
       <c r="C52" s="4">
         <v>47717462.320000052</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52" s="4">
+        <v>21684105.199999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>45383</v>
       </c>
@@ -1111,8 +1743,11 @@
       <c r="C53" s="4">
         <v>48845016.360000037</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53" s="4">
+        <v>22430452.140000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>45413</v>
       </c>
@@ -1122,8 +1757,11 @@
       <c r="C54" s="4">
         <v>50187063.050000057</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54" s="4">
+        <v>22508034.77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>45444</v>
       </c>
@@ -1133,8 +1771,11 @@
       <c r="C55" s="4">
         <v>50861531.570000045</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55" s="4">
+        <v>22466090.66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>45474</v>
       </c>
@@ -1144,8 +1785,11 @@
       <c r="C56" s="4">
         <v>51934196.490000002</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56" s="4">
+        <v>21190545.710000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>45505</v>
       </c>
@@ -1155,8 +1799,11 @@
       <c r="C57" s="4">
         <v>52190196.599999979</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57" s="4">
+        <v>21620685.690000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>45536</v>
       </c>
@@ -1166,8 +1813,11 @@
       <c r="C58" s="4">
         <v>52687295.450000055</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58" s="4">
+        <v>22887966.73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>45566</v>
       </c>
@@ -1177,8 +1827,11 @@
       <c r="C59" s="4">
         <v>53103043.679999895</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59" s="4">
+        <v>23769506.559999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>45597</v>
       </c>
@@ -1188,8 +1841,11 @@
       <c r="C60" s="4">
         <v>53540155.64000003</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60" s="4">
+        <v>24872451.98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>45627</v>
       </c>
@@ -1199,8 +1855,11 @@
       <c r="C61" s="4">
         <v>53778942.280000269</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61" s="4">
+        <v>25578321.34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>45658</v>
       </c>
@@ -1210,8 +1869,11 @@
       <c r="C62" s="4">
         <v>53416771.640000127</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62" s="4">
+        <v>25352781.300000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>45689</v>
       </c>
@@ -1221,8 +1883,11 @@
       <c r="C63" s="4">
         <v>52779524.890000112</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63" s="4">
+        <v>24961174.809999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>45717</v>
       </c>
@@ -1232,8 +1897,11 @@
       <c r="C64" s="4">
         <v>52661524.240000062</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D64" s="4">
+        <v>24941869.420000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>45748</v>
       </c>
@@ -1243,8 +1911,11 @@
       <c r="C65" s="4">
         <v>52995704.329999879</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D65" s="4">
+        <v>25442128.399999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>45778</v>
       </c>
@@ -1254,8 +1925,11 @@
       <c r="C66" s="4">
         <v>52854286.430000156</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66" s="4">
+        <v>27065486.949999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>45809</v>
       </c>
@@ -1265,8 +1939,11 @@
       <c r="C67" s="4">
         <v>53933005.649999872</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67" s="4">
+        <v>26432051.59</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>45839</v>
       </c>
@@ -1276,8 +1953,11 @@
       <c r="C68" s="4">
         <v>54609323.720000036</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68" s="4">
+        <v>25683360.210000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>45870</v>
       </c>
@@ -1287,8 +1967,11 @@
       <c r="C69" s="4">
         <v>54780310.699999936</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D69" s="4">
+        <v>26026852.84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>45901</v>
       </c>
@@ -1298,8 +1981,11 @@
       <c r="C70" s="4">
         <v>54904519.549999997</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70" s="4">
+        <v>26569897.030000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>45931</v>
       </c>
@@ -1309,8 +1995,11 @@
       <c r="C71" s="4">
         <v>54480654.780000195</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D71" s="4">
+        <v>27639360.579999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>45962</v>
       </c>
@@ -1320,8 +2009,11 @@
       <c r="C72" s="4">
         <v>54840118.230000004</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72" s="4">
+        <v>27586508.82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>45992</v>
       </c>
@@ -1331,8 +2023,11 @@
       <c r="C73" s="4">
         <v>54691253.479999982</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D73" s="4">
+        <v>26924849.649999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>46023</v>
       </c>
@@ -1342,18 +2037,653 @@
       <c r="C74" s="4">
         <v>52899193.469999924</v>
       </c>
+      <c r="D74" s="4">
+        <v>26868399.550000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B75" s="4">
+        <v>36854518.630000003</v>
+      </c>
+      <c r="C75" s="4">
+        <v>52562993.460000135</v>
+      </c>
+      <c r="D75" s="4">
+        <v>26562210.800000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B76" s="4">
+        <v>37202886.020000003</v>
+      </c>
+      <c r="C76" s="4">
+        <v>52362424.45000001</v>
+      </c>
+      <c r="D76" s="4">
+        <v>28216914.34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B77" s="4">
+        <v>36748697.700000003</v>
+      </c>
+      <c r="C77" s="4">
+        <v>53043857.479999878</v>
+      </c>
+      <c r="D77" s="4">
+        <v>29083752.07</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:C74">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="21" priority="17">
       <formula>#REF!&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:C74">
-    <cfRule type="expression" dxfId="0" priority="6">
+  <conditionalFormatting sqref="A2:C74 A75:A77">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>#REF!&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D38 D41:D74">
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>D$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41:D74 D2:D38">
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>D$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>D$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39">
+    <cfRule type="expression" dxfId="10" priority="10">
+      <formula>D$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>D$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40">
+    <cfRule type="expression" dxfId="8" priority="8">
+      <formula>D$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75:D77">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>B$4&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75:D77">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>B$4&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0E7BEA6-8AA8-4715-BB23-7A333036507C}">
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="8">
+        <v>83</v>
+      </c>
+      <c r="C2" s="8">
+        <v>83</v>
+      </c>
+      <c r="D2" s="8">
+        <v>83</v>
+      </c>
+      <c r="E2" s="8">
+        <v>83</v>
+      </c>
+      <c r="F2" s="8">
+        <v>83</v>
+      </c>
+      <c r="G2" s="8">
+        <v>83</v>
+      </c>
+      <c r="H2" s="8">
+        <v>83</v>
+      </c>
+      <c r="I2" s="8">
+        <v>83</v>
+      </c>
+      <c r="J2" s="8">
+        <v>83</v>
+      </c>
+      <c r="K2" s="8">
+        <v>83</v>
+      </c>
+      <c r="L2" s="8">
+        <v>83</v>
+      </c>
+      <c r="M2" s="8">
+        <v>83</v>
+      </c>
+      <c r="N2" s="8">
+        <v>83</v>
+      </c>
+      <c r="O2" s="8">
+        <v>83</v>
+      </c>
+      <c r="P2" s="8">
+        <v>83</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>83</v>
+      </c>
+      <c r="R2" s="8">
+        <v>83</v>
+      </c>
+      <c r="S2" s="8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="8">
+        <v>9.2167709999999996</v>
+      </c>
+      <c r="C3" s="8">
+        <v>4.9112499999999999</v>
+      </c>
+      <c r="D3" s="8">
+        <v>18.580296000000001</v>
+      </c>
+      <c r="E3" s="8">
+        <v>9.4824000000000006E-2</v>
+      </c>
+      <c r="F3" s="8">
+        <v>8.7214460000000003</v>
+      </c>
+      <c r="G3" s="8">
+        <v>57.890360999999999</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3.469903</v>
+      </c>
+      <c r="I3" s="8">
+        <v>292162.7</v>
+      </c>
+      <c r="J3" s="8">
+        <v>-4.5662649999999996</v>
+      </c>
+      <c r="K3" s="8">
+        <v>9.0566270000000006</v>
+      </c>
+      <c r="L3" s="8">
+        <v>693.43373499999996</v>
+      </c>
+      <c r="M3" s="8">
+        <v>8.5228970000000004</v>
+      </c>
+      <c r="N3" s="8">
+        <v>60.500644000000001</v>
+      </c>
+      <c r="O3" s="8">
+        <v>819.50306899999998</v>
+      </c>
+      <c r="P3" s="8">
+        <v>5.8216869999999998</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>29.238455999999999</v>
+      </c>
+      <c r="R3" s="8">
+        <v>124591.810361</v>
+      </c>
+      <c r="S3" s="8">
+        <v>104445.318313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="8">
+        <v>3.7892869999999998</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2.3333249999999999</v>
+      </c>
+      <c r="D4" s="8">
+        <v>7.18574</v>
+      </c>
+      <c r="E4" s="8">
+        <v>7.9121999999999998E-2</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1.2739119999999999</v>
+      </c>
+      <c r="G4" s="8">
+        <v>2.0237379999999998</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.81988799999999995</v>
+      </c>
+      <c r="I4" s="8">
+        <v>462542.1</v>
+      </c>
+      <c r="J4" s="8">
+        <v>4.9583700000000004</v>
+      </c>
+      <c r="K4" s="8">
+        <v>3.5632679999999999</v>
+      </c>
+      <c r="L4" s="8">
+        <v>299.311331</v>
+      </c>
+      <c r="M4" s="8">
+        <v>3.9418120000000001</v>
+      </c>
+      <c r="N4" s="8">
+        <v>14.862208000000001</v>
+      </c>
+      <c r="O4" s="8">
+        <v>284.90052800000001</v>
+      </c>
+      <c r="P4" s="8">
+        <v>1.2785329999999999</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>4.6439940000000002</v>
+      </c>
+      <c r="R4" s="8">
+        <v>42775.17095</v>
+      </c>
+      <c r="S4" s="8">
+        <v>36354.763740000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="8">
+        <v>2.2642679999999999</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.97598300000000004</v>
+      </c>
+      <c r="D5" s="8">
+        <v>2.6106669999999998</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.2423999999999999E-2</v>
+      </c>
+      <c r="F5" s="8">
+        <v>5.48</v>
+      </c>
+      <c r="G5" s="8">
+        <v>52.5</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1.8801460000000001</v>
+      </c>
+      <c r="I5" s="8">
+        <v>35698</v>
+      </c>
+      <c r="J5" s="8">
+        <v>-10.8</v>
+      </c>
+      <c r="K5" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="L5" s="8">
+        <v>71</v>
+      </c>
+      <c r="M5" s="8">
+        <v>1.1055440000000001</v>
+      </c>
+      <c r="N5" s="8">
+        <v>5.7000479999999998</v>
+      </c>
+      <c r="O5" s="8">
+        <v>546.93334400000003</v>
+      </c>
+      <c r="P5" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>15.311515</v>
+      </c>
+      <c r="R5" s="8">
+        <v>58606.97</v>
+      </c>
+      <c r="S5" s="8">
+        <v>58744.49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="B6" s="8">
+        <v>7.2864019999999998</v>
+      </c>
+      <c r="C6" s="8">
+        <v>3.8431320000000002</v>
+      </c>
+      <c r="D6" s="8">
+        <v>14.886592</v>
+      </c>
+      <c r="E6" s="8">
+        <v>6.0641E-2</v>
+      </c>
+      <c r="F6" s="8">
+        <v>8.4</v>
+      </c>
+      <c r="G6" s="8">
+        <v>56.55</v>
+      </c>
+      <c r="H6" s="8">
+        <v>3.0157919999999998</v>
+      </c>
+      <c r="I6" s="8">
+        <v>122550</v>
+      </c>
+      <c r="J6" s="8">
+        <v>-7.9</v>
+      </c>
+      <c r="K6" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="L6" s="8">
+        <v>525</v>
+      </c>
+      <c r="M6" s="8">
+        <v>6.3720150000000002</v>
+      </c>
+      <c r="N6" s="8">
+        <v>54.093321000000003</v>
+      </c>
+      <c r="O6" s="8">
+        <v>723.11458800000003</v>
+      </c>
+      <c r="P6" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>26.735583999999999</v>
+      </c>
+      <c r="R6" s="8">
+        <v>98283.32</v>
+      </c>
+      <c r="S6" s="8">
+        <v>84010.994999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="B7" s="8">
+        <v>8.6309660000000008</v>
+      </c>
+      <c r="C7" s="8">
+        <v>4.6112669999999998</v>
+      </c>
+      <c r="D7" s="8">
+        <v>18.534196000000001</v>
+      </c>
+      <c r="E7" s="8">
+        <v>7.8177999999999997E-2</v>
+      </c>
+      <c r="F7" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="G7" s="8">
+        <v>57.4</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3.366212</v>
+      </c>
+      <c r="I7" s="8">
+        <v>160717</v>
+      </c>
+      <c r="J7" s="8">
+        <v>-5.4</v>
+      </c>
+      <c r="K7" s="8">
+        <v>8.4</v>
+      </c>
+      <c r="L7" s="8">
+        <v>640</v>
+      </c>
+      <c r="M7" s="8">
+        <v>7.5566019999999998</v>
+      </c>
+      <c r="N7" s="8">
+        <v>63.320323999999999</v>
+      </c>
+      <c r="O7" s="8">
+        <v>747.02132099999994</v>
+      </c>
+      <c r="P7" s="8">
+        <v>5.9</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>29.796213000000002</v>
+      </c>
+      <c r="R7" s="8">
+        <v>116530.72</v>
+      </c>
+      <c r="S7" s="8">
+        <v>93461.92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="8">
+        <v>10.435375000000001</v>
+      </c>
+      <c r="C8" s="8">
+        <v>5.5113669999999999</v>
+      </c>
+      <c r="D8" s="8">
+        <v>20.737124999999999</v>
+      </c>
+      <c r="E8" s="8">
+        <v>9.6572000000000005E-2</v>
+      </c>
+      <c r="F8" s="8">
+        <v>9.2050000000000001</v>
+      </c>
+      <c r="G8" s="8">
+        <v>59.15</v>
+      </c>
+      <c r="H8" s="8">
+        <v>3.6880510000000002</v>
+      </c>
+      <c r="I8" s="8">
+        <v>237398</v>
+      </c>
+      <c r="J8" s="8">
+        <v>-2.9</v>
+      </c>
+      <c r="K8" s="8">
+        <v>10.4</v>
+      </c>
+      <c r="L8" s="8">
+        <v>790.5</v>
+      </c>
+      <c r="M8" s="8">
+        <v>10.000598</v>
+      </c>
+      <c r="N8" s="8">
+        <v>69.384799999999998</v>
+      </c>
+      <c r="O8" s="8">
+        <v>810.43318399999998</v>
+      </c>
+      <c r="P8" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>32.701011000000001</v>
+      </c>
+      <c r="R8" s="8">
+        <v>140266.16500000001</v>
+      </c>
+      <c r="S8" s="8">
+        <v>113634.72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="8">
+        <v>33.903920999999997</v>
+      </c>
+      <c r="C9" s="8">
+        <v>20.495718</v>
+      </c>
+      <c r="D9" s="8">
+        <v>58.337671999999998</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.565052</v>
+      </c>
+      <c r="F9" s="8">
+        <v>14.23</v>
+      </c>
+      <c r="G9" s="8">
+        <v>64.3</v>
+      </c>
+      <c r="H9" s="8">
+        <v>7.093153</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3177416</v>
+      </c>
+      <c r="J9" s="8">
+        <v>15.4</v>
+      </c>
+      <c r="K9" s="8">
+        <v>25.3</v>
+      </c>
+      <c r="L9" s="8">
+        <v>1985</v>
+      </c>
+      <c r="M9" s="8">
+        <v>27.060324999999999</v>
+      </c>
+      <c r="N9" s="8">
+        <v>89.370503999999997</v>
+      </c>
+      <c r="O9" s="8">
+        <v>2466.7168109999998</v>
+      </c>
+      <c r="P9" s="8">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>37.893045999999998</v>
+      </c>
+      <c r="R9" s="8">
+        <v>352661.15</v>
+      </c>
+      <c r="S9" s="8">
+        <v>320317.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>